--- a/Team-Data/2008-09/12-25-2008-09.xlsx
+++ b/Team-Data/2008-09/12-25-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
         <v>6</v>
@@ -763,19 +830,19 @@
         <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -787,7 +854,7 @@
         <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
@@ -796,13 +863,13 @@
         <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -814,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -846,22 +913,22 @@
         <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.897</v>
+        <v>0.931</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.486</v>
@@ -870,31 +937,31 @@
         <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O3" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="P3" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.765</v>
+        <v>0.76</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V3" t="n">
         <v>16.3</v>
@@ -903,25 +970,25 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.1</v>
+        <v>102.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -939,7 +1006,7 @@
         <v>10</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -951,28 +1018,28 @@
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>29</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -993,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1136,7 +1203,7 @@
         <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.464</v>
       </c>
       <c r="H5" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>84.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W5" t="n">
         <v>7.8</v>
@@ -1270,22 +1337,22 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.1</v>
+        <v>100.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,16 +1364,16 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1315,28 +1382,28 @@
         <v>21</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT5" t="n">
         <v>12</v>
       </c>
-      <c r="AS5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
       <c r="AU5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
@@ -1345,7 +1412,7 @@
         <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>24</v>
@@ -1354,13 +1421,13 @@
         <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -1392,88 +1459,88 @@
         <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.893</v>
+        <v>0.857</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J6" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.481</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.339</v>
       </c>
       <c r="O6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>42.1</v>
       </c>
       <c r="U6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>8</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AA6" t="n">
         <v>21</v>
       </c>
-      <c r="V6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>20.7</v>
-      </c>
       <c r="AB6" t="n">
-        <v>102.6</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1485,25 +1552,25 @@
         <v>4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM6" t="n">
         <v>9</v>
       </c>
-      <c r="AM6" t="n">
-        <v>6</v>
-      </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="n">
         <v>12</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
@@ -1512,13 +1579,13 @@
         <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AV6" t="n">
         <v>2</v>
@@ -1530,16 +1597,16 @@
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -1571,19 +1638,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.607</v>
+        <v>0.593</v>
       </c>
       <c r="H7" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I7" t="n">
         <v>38</v>
@@ -1592,7 +1659,7 @@
         <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L7" t="n">
         <v>6.7</v>
@@ -1604,28 +1671,28 @@
         <v>0.331</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8</v>
+        <v>0.799</v>
       </c>
       <c r="R7" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S7" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="T7" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W7" t="n">
         <v>7</v>
@@ -1634,25 +1701,25 @@
         <v>5.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA7" t="n">
         <v>19.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,22 +1728,22 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
       </c>
       <c r="AK7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
       </c>
       <c r="AM7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN7" t="n">
         <v>24</v>
@@ -1685,13 +1752,13 @@
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
@@ -1703,28 +1770,28 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>14</v>
@@ -1858,10 +1925,10 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1900,13 +1967,13 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
@@ -2022,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>10</v>
@@ -2034,7 +2101,7 @@
         <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
         <v>21</v>
@@ -2049,10 +2116,10 @@
         <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
         <v>23</v>
@@ -2064,7 +2131,7 @@
         <v>25</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>4</v>
@@ -2076,13 +2143,13 @@
         <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
         <v>21</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -2216,10 +2283,10 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM10" t="n">
         <v>14</v>
@@ -2228,13 +2295,13 @@
         <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2386,19 +2453,19 @@
         <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>25</v>
       </c>
       <c r="AJ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK11" t="n">
         <v>19</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>18</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2428,7 +2495,7 @@
         <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>12</v>
@@ -2437,7 +2504,7 @@
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
         <v>26</v>
@@ -2452,7 +2519,7 @@
         <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2583,7 +2650,7 @@
         <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
         <v>10</v>
@@ -2592,13 +2659,13 @@
         <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
@@ -2607,10 +2674,10 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>26</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2759,7 +2826,7 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2777,7 +2844,7 @@
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
@@ -2789,10 +2856,10 @@
         <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -2810,7 +2877,7 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -2872,40 +2939,40 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.37</v>
+        <v>0.376</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P14" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V14" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
@@ -2914,16 +2981,16 @@
         <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2947,13 +3014,13 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,16 +3029,16 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2983,13 +3050,13 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3117,7 +3184,7 @@
         <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
         <v>26</v>
@@ -3126,7 +3193,7 @@
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
         <v>26</v>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
         <v>14</v>
@@ -3144,10 +3211,10 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3168,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -3287,19 +3354,19 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>15</v>
@@ -3311,10 +3378,10 @@
         <v>16</v>
       </c>
       <c r="AL16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN16" t="n">
         <v>19</v>
@@ -3323,7 +3390,7 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
@@ -3335,7 +3402,7 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU16" t="n">
         <v>25</v>
@@ -3344,19 +3411,19 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.467</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,79 +3476,79 @@
         <v>36.3</v>
       </c>
       <c r="J17" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L17" t="n">
         <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R17" t="n">
         <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>31.1</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>44.1</v>
+        <v>43.7</v>
       </c>
       <c r="U17" t="n">
         <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
         <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
         <v>16</v>
@@ -3490,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>25</v>
@@ -3514,37 +3581,37 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
         <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>-7.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH18" t="n">
         <v>4</v>
@@ -3684,10 +3751,10 @@
         <v>28</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3699,7 +3766,7 @@
         <v>23</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3720,7 +3787,7 @@
         <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3848,22 +3915,22 @@
         <v>11</v>
       </c>
       <c r="AI19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="n">
         <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM19" t="n">
         <v>6</v>
       </c>
-      <c r="AM19" t="n">
-        <v>5</v>
-      </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3881,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3893,7 +3960,7 @@
         <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
@@ -3905,10 +3972,10 @@
         <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -3937,94 +4004,94 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" t="n">
         <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.64</v>
+        <v>0.667</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="J20" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.397</v>
+        <v>0.402</v>
       </c>
       <c r="O20" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="n">
         <v>0.806</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4036,46 +4103,46 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
         <v>4</v>
@@ -4087,10 +4154,10 @@
         <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -4197,22 +4264,22 @@
         <v>-3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ21" t="n">
         <v>2</v>
@@ -4230,10 +4297,10 @@
         <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
         <v>4</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4409,10 +4476,10 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP22" t="n">
         <v>16</v>
@@ -4421,7 +4488,7 @@
         <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
         <v>19</v>
@@ -4436,10 +4503,10 @@
         <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.793</v>
+        <v>0.786</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J23" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L23" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M23" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="O23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P23" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
         <v>18.6</v>
@@ -4543,28 +4610,28 @@
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y23" t="n">
         <v>3.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>100.6</v>
+        <v>101.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>11</v>
@@ -4627,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>7</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -4743,22 +4810,22 @@
         <v>-1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF24" t="n">
         <v>18</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>19</v>
       </c>
       <c r="AG24" t="n">
         <v>19</v>
       </c>
       <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
         <v>20</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>19</v>
       </c>
       <c r="AJ24" t="n">
         <v>11</v>
@@ -4779,7 +4846,7 @@
         <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>24</v>
@@ -4788,13 +4855,13 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
         <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV24" t="n">
         <v>27</v>
@@ -4809,7 +4876,7 @@
         <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.593</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J25" t="n">
         <v>76.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M25" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="N25" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="O25" t="n">
         <v>19.9</v>
@@ -4886,22 +4953,22 @@
         <v>26.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R25" t="n">
         <v>9.1</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40</v>
       </c>
       <c r="U25" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W25" t="n">
         <v>6.4</v>
@@ -4913,37 +4980,37 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
         <v>21.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>102.9</v>
+        <v>103.3</v>
       </c>
       <c r="AC25" t="n">
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4952,10 +5019,10 @@
         <v>9</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4970,13 +5037,13 @@
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
         <v>28</v>
@@ -4988,7 +5055,7 @@
         <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
         <v>10</v>
@@ -5000,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -5044,73 +5111,73 @@
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>79.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>20.3</v>
+        <v>20.8</v>
       </c>
       <c r="N26" t="n">
         <v>0.392</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="P26" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R26" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
         <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
         <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
         <v>9</v>
@@ -5122,28 +5189,28 @@
         <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
         <v>10</v>
@@ -5152,37 +5219,37 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB26" t="n">
         <v>14</v>
       </c>
-      <c r="BA26" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>13</v>
-      </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5310,7 +5377,7 @@
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL27" t="n">
         <v>22</v>
@@ -5322,10 +5389,10 @@
         <v>27</v>
       </c>
       <c r="AO27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ27" t="n">
         <v>9</v>
@@ -5358,7 +5425,7 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -5393,52 +5460,52 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>0.655</v>
+        <v>0.643</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J28" t="n">
-        <v>79.2</v>
+        <v>78.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.751</v>
+        <v>0.754</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T28" t="n">
         <v>40.9</v>
@@ -5447,40 +5514,40 @@
         <v>21.6</v>
       </c>
       <c r="V28" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="W28" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="X28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF28" t="n">
         <v>6</v>
       </c>
       <c r="AG28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH28" t="n">
         <v>3</v>
@@ -5489,19 +5556,19 @@
         <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>4</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5522,7 +5589,7 @@
         <v>21</v>
       </c>
       <c r="AU28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5534,7 +5601,7 @@
         <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5671,10 +5738,10 @@
         <v>28</v>
       </c>
       <c r="AJ29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK29" t="n">
         <v>20</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>16</v>
@@ -5686,10 +5753,10 @@
         <v>7</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,10 +5765,10 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
@@ -5710,7 +5777,7 @@
         <v>6</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
         <v>11</v>
@@ -5719,13 +5786,13 @@
         <v>16</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
         <v>18</v>
       </c>
       <c r="BB29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.44</v>
       </c>
       <c r="L31" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M31" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.322</v>
+        <v>0.32</v>
       </c>
       <c r="O31" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="P31" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R31" t="n">
         <v>11.6</v>
       </c>
       <c r="S31" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T31" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
         <v>13.7</v>
@@ -6002,28 +6069,28 @@
         <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z31" t="n">
         <v>21.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6032,7 +6099,7 @@
         <v>17</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6041,22 +6108,22 @@
         <v>24</v>
       </c>
       <c r="AL31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AN31" t="n">
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>14</v>
@@ -6065,13 +6132,13 @@
         <v>27</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
         <v>13</v>
@@ -6086,10 +6153,10 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-25-2008-09</t>
+          <t>2008-12-25</t>
         </is>
       </c>
     </row>
